--- a/documentation/3D_Printing_Defect_Inspection_Results_Output.xlsx
+++ b/documentation/3D_Printing_Defect_Inspection_Results_Output.xlsx
@@ -693,32 +693,32 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>553</t>
+          <t>581</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>537</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>44</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>93.9%</t>
+          <t>92.4%</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>74.2%</t>
+          <t>73.1%</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>176.7 ms</t>
+          <t>207.0 ms</t>
         </is>
       </c>
     </row>
@@ -765,13 +765,13 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>502</v>
+        <v>512</v>
       </c>
       <c r="C10" s="12" t="n">
-        <v>0.9077757685352622</v>
+        <v>0.8812392426850258</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>0.7569454183266934</v>
+        <v>0.7565957031250002</v>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
         </is>
       </c>
       <c r="B11" s="15" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C11" s="16" t="n">
-        <v>0.03074141048824593</v>
+        <v>0.04647160068846816</v>
       </c>
       <c r="D11" s="16" t="n">
         <v>0</v>
@@ -803,42 +803,42 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>Normal / Good Print</t>
+          <t>Stringing</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>0.02893309222423146</v>
+        <v>0.0378657487091222</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>1</v>
+        <v>0.8850000000000001</v>
       </c>
       <c r="E12" s="18" t="inlineStr">
         <is>
-          <t>NOMINAL (Passing Quality)</t>
+          <t>LOW (Cosmetic Cleanup)</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>Stringing</t>
+          <t>Normal / Good Print</t>
         </is>
       </c>
       <c r="B13" s="15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C13" s="16" t="n">
-        <v>0.027124773960217</v>
+        <v>0.02753872633390706</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>0.8849999999999999</v>
+        <v>1</v>
       </c>
       <c r="E13" s="17" t="inlineStr">
         <is>
-          <t>LOW (Cosmetic Cleanup)</t>
+          <t>NOMINAL (Passing Quality)</t>
         </is>
       </c>
     </row>
@@ -849,13 +849,13 @@
         </is>
       </c>
       <c r="B14" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>0.003616636528028933</v>
+        <v>0.005163511187607574</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>0.6118</v>
+        <v>0.6735000000000001</v>
       </c>
       <c r="E14" s="18" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>1</v>
       </c>
       <c r="C15" s="16" t="n">
-        <v>0.001808318264014466</v>
+        <v>0.001721170395869191</v>
       </c>
       <c r="D15" s="16" t="n">
         <v>0</v>
@@ -927,16 +927,16 @@
         </is>
       </c>
       <c r="B20" s="11" t="n">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>0.5614035087719298</v>
+        <v>0.5526315789473685</v>
       </c>
       <c r="E20" s="20" t="n">
-        <v>1153.514385964912</v>
+        <v>1154.265131578947</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
@@ -965,16 +965,16 @@
         </is>
       </c>
       <c r="B22" s="11" t="n">
-        <v>493</v>
+        <v>502</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>492</v>
+        <v>501</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>0.002028397565922921</v>
+        <v>0.00199203187250996</v>
       </c>
       <c r="E22" s="20" t="n">
-        <v>64.8075050709939</v>
+        <v>64.85743027888446</v>
       </c>
     </row>
   </sheetData>
@@ -991,7 +991,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K556"/>
+  <dimension ref="A1:K584"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1010,7 +1010,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>MASTER INSPECTION RUNS LOG (553 TOTAL SESSIONS RECORDED)</t>
+          <t>MASTER INSPECTION RUNS LOG (581 TOTAL SESSIONS RECORDED)</t>
         </is>
       </c>
     </row>
@@ -28166,6 +28166,1378 @@
       <c r="K556" s="22" t="inlineStr">
         <is>
           <t>Live Camera 1 (Auto Alert)</t>
+        </is>
+      </c>
+    </row>
+    <row r="557" ht="19" customHeight="1">
+      <c r="A557" s="17" t="n">
+        <v>554</v>
+      </c>
+      <c r="B557" s="17" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="C557" s="27" t="inlineStr">
+        <is>
+          <t>20260910_142446_43ff5d06_auto_defect_20260910_142446.jpg</t>
+        </is>
+      </c>
+      <c r="D557" s="27" t="inlineStr">
+        <is>
+          <t>20260910_142446_43ff5d06_auto_defect_20260910_142446.jpg</t>
+        </is>
+      </c>
+      <c r="E557" s="27" t="inlineStr">
+        <is>
+          <t>Spaghetti Failure</t>
+        </is>
+      </c>
+      <c r="F557" s="28" t="n">
+        <v>0.8611</v>
+      </c>
+      <c r="G557" s="24" t="inlineStr">
+        <is>
+          <t>DEFECT</t>
+        </is>
+      </c>
+      <c r="H557" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I557" s="31" t="n">
+        <v>99.23</v>
+      </c>
+      <c r="J557" s="17" t="inlineStr">
+        <is>
+          <t>2026-09-10 08:54:46</t>
+        </is>
+      </c>
+      <c r="K557" s="27" t="inlineStr">
+        <is>
+          <t>Live Camera 1 (Auto Alert)</t>
+        </is>
+      </c>
+    </row>
+    <row r="558" ht="19" customHeight="1">
+      <c r="A558" s="18" t="n">
+        <v>555</v>
+      </c>
+      <c r="B558" s="18" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="C558" s="22" t="inlineStr">
+        <is>
+          <t>20260910_142450_d19e3eda_auto_defect_20260910_142450.jpg</t>
+        </is>
+      </c>
+      <c r="D558" s="22" t="inlineStr">
+        <is>
+          <t>20260910_142450_d19e3eda_auto_defect_20260910_142450.jpg</t>
+        </is>
+      </c>
+      <c r="E558" s="22" t="inlineStr">
+        <is>
+          <t>Spaghetti Failure</t>
+        </is>
+      </c>
+      <c r="F558" s="23" t="n">
+        <v>0.6252</v>
+      </c>
+      <c r="G558" s="24" t="inlineStr">
+        <is>
+          <t>DEFECT</t>
+        </is>
+      </c>
+      <c r="H558" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I558" s="26" t="n">
+        <v>120.11</v>
+      </c>
+      <c r="J558" s="18" t="inlineStr">
+        <is>
+          <t>2026-09-10 08:54:50</t>
+        </is>
+      </c>
+      <c r="K558" s="22" t="inlineStr">
+        <is>
+          <t>Live Camera 1 (Auto Alert)</t>
+        </is>
+      </c>
+    </row>
+    <row r="559" ht="19" customHeight="1">
+      <c r="A559" s="17" t="n">
+        <v>556</v>
+      </c>
+      <c r="B559" s="17" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="C559" s="27" t="inlineStr">
+        <is>
+          <t>20260910_142453_515733fd_auto_defect_20260910_142453.jpg</t>
+        </is>
+      </c>
+      <c r="D559" s="27" t="inlineStr">
+        <is>
+          <t>20260910_142453_515733fd_auto_defect_20260910_142453.jpg</t>
+        </is>
+      </c>
+      <c r="E559" s="27" t="inlineStr">
+        <is>
+          <t>Spaghetti Failure</t>
+        </is>
+      </c>
+      <c r="F559" s="28" t="n">
+        <v>0.5371</v>
+      </c>
+      <c r="G559" s="24" t="inlineStr">
+        <is>
+          <t>DEFECT</t>
+        </is>
+      </c>
+      <c r="H559" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I559" s="31" t="n">
+        <v>112.84</v>
+      </c>
+      <c r="J559" s="17" t="inlineStr">
+        <is>
+          <t>2026-09-10 08:54:53</t>
+        </is>
+      </c>
+      <c r="K559" s="27" t="inlineStr">
+        <is>
+          <t>Live Camera 1 (Auto Alert)</t>
+        </is>
+      </c>
+    </row>
+    <row r="560" ht="19" customHeight="1">
+      <c r="A560" s="18" t="n">
+        <v>557</v>
+      </c>
+      <c r="B560" s="18" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="C560" s="22" t="inlineStr">
+        <is>
+          <t>upload_20260910_151018_9dfd332f_test_print.jpg</t>
+        </is>
+      </c>
+      <c r="D560" s="22" t="inlineStr">
+        <is>
+          <t>annotated_20260910_151029_1e5c04db_upload_20260910_151018_9dfd332f_test_print.jpg</t>
+        </is>
+      </c>
+      <c r="E560" s="22" t="inlineStr">
+        <is>
+          <t>No Defect Detected</t>
+        </is>
+      </c>
+      <c r="F560" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G560" s="29" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="H560" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I560" s="26" t="n">
+        <v>11350.81</v>
+      </c>
+      <c r="J560" s="18" t="inlineStr">
+        <is>
+          <t>2026-09-10 09:40:29</t>
+        </is>
+      </c>
+      <c r="K560" s="22" t="inlineStr">
+        <is>
+          <t>Web Image Upload</t>
+        </is>
+      </c>
+    </row>
+    <row r="561" ht="19" customHeight="1">
+      <c r="A561" s="17" t="n">
+        <v>558</v>
+      </c>
+      <c r="B561" s="17" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="C561" s="27" t="inlineStr">
+        <is>
+          <t>test_sample.jpg</t>
+        </is>
+      </c>
+      <c r="D561" s="27" t="inlineStr">
+        <is>
+          <t>annotated_test_sample.jpg</t>
+        </is>
+      </c>
+      <c r="E561" s="27" t="inlineStr">
+        <is>
+          <t>Stringing</t>
+        </is>
+      </c>
+      <c r="F561" s="28" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="G561" s="24" t="inlineStr">
+        <is>
+          <t>DEFECT</t>
+        </is>
+      </c>
+      <c r="H561" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I561" s="31" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="J561" s="17" t="inlineStr">
+        <is>
+          <t>2026-09-10 09:40:30</t>
+        </is>
+      </c>
+      <c r="K561" s="27" t="inlineStr">
+        <is>
+          <t>Unit Test</t>
+        </is>
+      </c>
+    </row>
+    <row r="562" ht="19" customHeight="1">
+      <c r="A562" s="18" t="n">
+        <v>559</v>
+      </c>
+      <c r="B562" s="18" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="C562" s="22" t="inlineStr">
+        <is>
+          <t>upload_20260910_151031_66182a3c_test_print.png</t>
+        </is>
+      </c>
+      <c r="D562" s="22" t="inlineStr">
+        <is>
+          <t>annotated_20260910_151031_5c16b998_upload_20260910_151031_66182a3c_test_print.png</t>
+        </is>
+      </c>
+      <c r="E562" s="22" t="inlineStr">
+        <is>
+          <t>No Defect Detected</t>
+        </is>
+      </c>
+      <c r="F562" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G562" s="29" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="H562" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I562" s="26" t="n">
+        <v>500.19</v>
+      </c>
+      <c r="J562" s="18" t="inlineStr">
+        <is>
+          <t>2026-09-10 09:40:31</t>
+        </is>
+      </c>
+      <c r="K562" s="22" t="inlineStr">
+        <is>
+          <t>Web Image Upload</t>
+        </is>
+      </c>
+    </row>
+    <row r="563" ht="19" customHeight="1">
+      <c r="A563" s="17" t="n">
+        <v>560</v>
+      </c>
+      <c r="B563" s="17" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="C563" s="27" t="inlineStr">
+        <is>
+          <t>upload_20260910_151309_7d1122e8_test_print.jpg</t>
+        </is>
+      </c>
+      <c r="D563" s="27" t="inlineStr">
+        <is>
+          <t>annotated_20260910_151311_3e496e8f_upload_20260910_151309_7d1122e8_test_print.jpg</t>
+        </is>
+      </c>
+      <c r="E563" s="27" t="inlineStr">
+        <is>
+          <t>No Defect Detected</t>
+        </is>
+      </c>
+      <c r="F563" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G563" s="29" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="H563" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I563" s="31" t="n">
+        <v>1827.73</v>
+      </c>
+      <c r="J563" s="17" t="inlineStr">
+        <is>
+          <t>2026-09-10 09:43:11</t>
+        </is>
+      </c>
+      <c r="K563" s="27" t="inlineStr">
+        <is>
+          <t>Web Image Upload</t>
+        </is>
+      </c>
+    </row>
+    <row r="564" ht="19" customHeight="1">
+      <c r="A564" s="18" t="n">
+        <v>561</v>
+      </c>
+      <c r="B564" s="18" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="C564" s="22" t="inlineStr">
+        <is>
+          <t>test_sample.jpg</t>
+        </is>
+      </c>
+      <c r="D564" s="22" t="inlineStr">
+        <is>
+          <t>annotated_test_sample.jpg</t>
+        </is>
+      </c>
+      <c r="E564" s="22" t="inlineStr">
+        <is>
+          <t>Stringing</t>
+        </is>
+      </c>
+      <c r="F564" s="23" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="G564" s="24" t="inlineStr">
+        <is>
+          <t>DEFECT</t>
+        </is>
+      </c>
+      <c r="H564" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I564" s="26" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="J564" s="18" t="inlineStr">
+        <is>
+          <t>2026-09-10 09:43:11</t>
+        </is>
+      </c>
+      <c r="K564" s="22" t="inlineStr">
+        <is>
+          <t>Unit Test</t>
+        </is>
+      </c>
+    </row>
+    <row r="565" ht="19" customHeight="1">
+      <c r="A565" s="17" t="n">
+        <v>562</v>
+      </c>
+      <c r="B565" s="17" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="C565" s="27" t="inlineStr">
+        <is>
+          <t>upload_20260910_151311_5ae121c3_test_print.png</t>
+        </is>
+      </c>
+      <c r="D565" s="27" t="inlineStr">
+        <is>
+          <t>annotated_20260910_151312_47400312_upload_20260910_151311_5ae121c3_test_print.png</t>
+        </is>
+      </c>
+      <c r="E565" s="27" t="inlineStr">
+        <is>
+          <t>No Defect Detected</t>
+        </is>
+      </c>
+      <c r="F565" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G565" s="29" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="H565" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I565" s="31" t="n">
+        <v>115.4</v>
+      </c>
+      <c r="J565" s="17" t="inlineStr">
+        <is>
+          <t>2026-09-10 09:43:12</t>
+        </is>
+      </c>
+      <c r="K565" s="27" t="inlineStr">
+        <is>
+          <t>Web Image Upload</t>
+        </is>
+      </c>
+    </row>
+    <row r="566" ht="19" customHeight="1">
+      <c r="A566" s="18" t="n">
+        <v>563</v>
+      </c>
+      <c r="B566" s="18" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="C566" s="22" t="inlineStr">
+        <is>
+          <t>upload_20260910_151423_f1cd759c_test_print.jpg</t>
+        </is>
+      </c>
+      <c r="D566" s="22" t="inlineStr">
+        <is>
+          <t>annotated_20260910_151425_478647ee_upload_20260910_151423_f1cd759c_test_print.jpg</t>
+        </is>
+      </c>
+      <c r="E566" s="22" t="inlineStr">
+        <is>
+          <t>No Defect Detected</t>
+        </is>
+      </c>
+      <c r="F566" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G566" s="29" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="H566" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I566" s="26" t="n">
+        <v>1682.96</v>
+      </c>
+      <c r="J566" s="18" t="inlineStr">
+        <is>
+          <t>2026-09-10 09:44:25</t>
+        </is>
+      </c>
+      <c r="K566" s="22" t="inlineStr">
+        <is>
+          <t>Web Image Upload</t>
+        </is>
+      </c>
+    </row>
+    <row r="567" ht="19" customHeight="1">
+      <c r="A567" s="17" t="n">
+        <v>564</v>
+      </c>
+      <c r="B567" s="17" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="C567" s="27" t="inlineStr">
+        <is>
+          <t>test_sample.jpg</t>
+        </is>
+      </c>
+      <c r="D567" s="27" t="inlineStr">
+        <is>
+          <t>annotated_test_sample.jpg</t>
+        </is>
+      </c>
+      <c r="E567" s="27" t="inlineStr">
+        <is>
+          <t>Stringing</t>
+        </is>
+      </c>
+      <c r="F567" s="28" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="G567" s="24" t="inlineStr">
+        <is>
+          <t>DEFECT</t>
+        </is>
+      </c>
+      <c r="H567" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I567" s="31" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="J567" s="17" t="inlineStr">
+        <is>
+          <t>2026-09-10 09:44:25</t>
+        </is>
+      </c>
+      <c r="K567" s="27" t="inlineStr">
+        <is>
+          <t>Unit Test</t>
+        </is>
+      </c>
+    </row>
+    <row r="568" ht="19" customHeight="1">
+      <c r="A568" s="18" t="n">
+        <v>565</v>
+      </c>
+      <c r="B568" s="18" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="C568" s="22" t="inlineStr">
+        <is>
+          <t>upload_20260910_151425_9af20257_test_print.png</t>
+        </is>
+      </c>
+      <c r="D568" s="22" t="inlineStr">
+        <is>
+          <t>annotated_20260910_151425_afff9e8e_upload_20260910_151425_9af20257_test_print.png</t>
+        </is>
+      </c>
+      <c r="E568" s="22" t="inlineStr">
+        <is>
+          <t>No Defect Detected</t>
+        </is>
+      </c>
+      <c r="F568" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G568" s="29" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="H568" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I568" s="26" t="n">
+        <v>121.67</v>
+      </c>
+      <c r="J568" s="18" t="inlineStr">
+        <is>
+          <t>2026-09-10 09:44:25</t>
+        </is>
+      </c>
+      <c r="K568" s="22" t="inlineStr">
+        <is>
+          <t>Web Image Upload</t>
+        </is>
+      </c>
+    </row>
+    <row r="569" ht="19" customHeight="1">
+      <c r="A569" s="17" t="n">
+        <v>566</v>
+      </c>
+      <c r="B569" s="17" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="C569" s="27" t="inlineStr">
+        <is>
+          <t>upload_20260910_155206_330b3076_test_print.jpg</t>
+        </is>
+      </c>
+      <c r="D569" s="27" t="inlineStr">
+        <is>
+          <t>annotated_20260910_155210_7943ef14_upload_20260910_155206_330b3076_test_print.jpg</t>
+        </is>
+      </c>
+      <c r="E569" s="27" t="inlineStr">
+        <is>
+          <t>No Defect Detected</t>
+        </is>
+      </c>
+      <c r="F569" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G569" s="29" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="H569" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I569" s="31" t="n">
+        <v>3455.64</v>
+      </c>
+      <c r="J569" s="17" t="inlineStr">
+        <is>
+          <t>2026-09-10 10:22:10</t>
+        </is>
+      </c>
+      <c r="K569" s="27" t="inlineStr">
+        <is>
+          <t>Web Image Upload</t>
+        </is>
+      </c>
+    </row>
+    <row r="570" ht="19" customHeight="1">
+      <c r="A570" s="18" t="n">
+        <v>567</v>
+      </c>
+      <c r="B570" s="18" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="C570" s="22" t="inlineStr">
+        <is>
+          <t>test_sample.jpg</t>
+        </is>
+      </c>
+      <c r="D570" s="22" t="inlineStr">
+        <is>
+          <t>annotated_test_sample.jpg</t>
+        </is>
+      </c>
+      <c r="E570" s="22" t="inlineStr">
+        <is>
+          <t>Stringing</t>
+        </is>
+      </c>
+      <c r="F570" s="23" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="G570" s="24" t="inlineStr">
+        <is>
+          <t>DEFECT</t>
+        </is>
+      </c>
+      <c r="H570" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I570" s="26" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="J570" s="18" t="inlineStr">
+        <is>
+          <t>2026-09-10 10:22:11</t>
+        </is>
+      </c>
+      <c r="K570" s="22" t="inlineStr">
+        <is>
+          <t>Unit Test</t>
+        </is>
+      </c>
+    </row>
+    <row r="571" ht="19" customHeight="1">
+      <c r="A571" s="17" t="n">
+        <v>568</v>
+      </c>
+      <c r="B571" s="17" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="C571" s="27" t="inlineStr">
+        <is>
+          <t>upload_20260910_155211_e41cba57_test_print.png</t>
+        </is>
+      </c>
+      <c r="D571" s="27" t="inlineStr">
+        <is>
+          <t>annotated_20260910_155211_ba400768_upload_20260910_155211_e41cba57_test_print.png</t>
+        </is>
+      </c>
+      <c r="E571" s="27" t="inlineStr">
+        <is>
+          <t>No Defect Detected</t>
+        </is>
+      </c>
+      <c r="F571" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G571" s="29" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="H571" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I571" s="31" t="n">
+        <v>167.09</v>
+      </c>
+      <c r="J571" s="17" t="inlineStr">
+        <is>
+          <t>2026-09-10 10:22:11</t>
+        </is>
+      </c>
+      <c r="K571" s="27" t="inlineStr">
+        <is>
+          <t>Web Image Upload</t>
+        </is>
+      </c>
+    </row>
+    <row r="572" ht="19" customHeight="1">
+      <c r="A572" s="18" t="n">
+        <v>569</v>
+      </c>
+      <c r="B572" s="18" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="C572" s="22" t="inlineStr">
+        <is>
+          <t>upload_20260910_155351_64e18b3f_test_print.jpg</t>
+        </is>
+      </c>
+      <c r="D572" s="22" t="inlineStr">
+        <is>
+          <t>annotated_20260910_155353_3e93553d_upload_20260910_155351_64e18b3f_test_print.jpg</t>
+        </is>
+      </c>
+      <c r="E572" s="22" t="inlineStr">
+        <is>
+          <t>No Defect Detected</t>
+        </is>
+      </c>
+      <c r="F572" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G572" s="29" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="H572" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I572" s="26" t="n">
+        <v>1779.76</v>
+      </c>
+      <c r="J572" s="18" t="inlineStr">
+        <is>
+          <t>2026-09-10 10:23:53</t>
+        </is>
+      </c>
+      <c r="K572" s="22" t="inlineStr">
+        <is>
+          <t>Web Image Upload</t>
+        </is>
+      </c>
+    </row>
+    <row r="573" ht="19" customHeight="1">
+      <c r="A573" s="17" t="n">
+        <v>570</v>
+      </c>
+      <c r="B573" s="17" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="C573" s="27" t="inlineStr">
+        <is>
+          <t>test_sample.jpg</t>
+        </is>
+      </c>
+      <c r="D573" s="27" t="inlineStr">
+        <is>
+          <t>annotated_test_sample.jpg</t>
+        </is>
+      </c>
+      <c r="E573" s="27" t="inlineStr">
+        <is>
+          <t>Stringing</t>
+        </is>
+      </c>
+      <c r="F573" s="28" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="G573" s="24" t="inlineStr">
+        <is>
+          <t>DEFECT</t>
+        </is>
+      </c>
+      <c r="H573" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I573" s="31" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="J573" s="17" t="inlineStr">
+        <is>
+          <t>2026-09-10 10:23:53</t>
+        </is>
+      </c>
+      <c r="K573" s="27" t="inlineStr">
+        <is>
+          <t>Unit Test</t>
+        </is>
+      </c>
+    </row>
+    <row r="574" ht="19" customHeight="1">
+      <c r="A574" s="18" t="n">
+        <v>571</v>
+      </c>
+      <c r="B574" s="18" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="C574" s="22" t="inlineStr">
+        <is>
+          <t>upload_20260910_155353_ffe82544_test_print.png</t>
+        </is>
+      </c>
+      <c r="D574" s="22" t="inlineStr">
+        <is>
+          <t>annotated_20260910_155353_22848eb3_upload_20260910_155353_ffe82544_test_print.png</t>
+        </is>
+      </c>
+      <c r="E574" s="22" t="inlineStr">
+        <is>
+          <t>No Defect Detected</t>
+        </is>
+      </c>
+      <c r="F574" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G574" s="29" t="inlineStr">
+        <is>
+          <t>GOOD</t>
+        </is>
+      </c>
+      <c r="H574" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I574" s="26" t="n">
+        <v>71.65000000000001</v>
+      </c>
+      <c r="J574" s="18" t="inlineStr">
+        <is>
+          <t>2026-09-10 10:23:53</t>
+        </is>
+      </c>
+      <c r="K574" s="22" t="inlineStr">
+        <is>
+          <t>Web Image Upload</t>
+        </is>
+      </c>
+    </row>
+    <row r="575" ht="19" customHeight="1">
+      <c r="A575" s="17" t="n">
+        <v>572</v>
+      </c>
+      <c r="B575" s="17" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="C575" s="27" t="inlineStr">
+        <is>
+          <t>20260910_184118_5ff3fcbf_auto_defect_20260910_184118.jpg</t>
+        </is>
+      </c>
+      <c r="D575" s="27" t="inlineStr">
+        <is>
+          <t>20260910_184118_5ff3fcbf_auto_defect_20260910_184118.jpg</t>
+        </is>
+      </c>
+      <c r="E575" s="27" t="inlineStr">
+        <is>
+          <t>Spaghetti Failure</t>
+        </is>
+      </c>
+      <c r="F575" s="28" t="n">
+        <v>0.9859</v>
+      </c>
+      <c r="G575" s="24" t="inlineStr">
+        <is>
+          <t>DEFECT</t>
+        </is>
+      </c>
+      <c r="H575" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I575" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J575" s="17" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:11:18</t>
+        </is>
+      </c>
+      <c r="K575" s="27" t="inlineStr">
+        <is>
+          <t>Live Camera 0 (Auto Alert)</t>
+        </is>
+      </c>
+    </row>
+    <row r="576" ht="19" customHeight="1">
+      <c r="A576" s="18" t="n">
+        <v>573</v>
+      </c>
+      <c r="B576" s="18" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="C576" s="22" t="inlineStr">
+        <is>
+          <t>upload_20260910_184202_84b29c53_3d_pic.jpeg</t>
+        </is>
+      </c>
+      <c r="D576" s="22" t="inlineStr">
+        <is>
+          <t>annotated_20260910_184203_35e5df80_upload_20260910_184202_84b29c53_3d_pic.jpeg</t>
+        </is>
+      </c>
+      <c r="E576" s="22" t="inlineStr">
+        <is>
+          <t>Spaghetti Failure</t>
+        </is>
+      </c>
+      <c r="F576" s="23" t="n">
+        <v>0.8398</v>
+      </c>
+      <c r="G576" s="24" t="inlineStr">
+        <is>
+          <t>DEFECT</t>
+        </is>
+      </c>
+      <c r="H576" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I576" s="26" t="n">
+        <v>257.57</v>
+      </c>
+      <c r="J576" s="18" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:12:03</t>
+        </is>
+      </c>
+      <c r="K576" s="22" t="inlineStr">
+        <is>
+          <t>Web Image Upload</t>
+        </is>
+      </c>
+    </row>
+    <row r="577" ht="19" customHeight="1">
+      <c r="A577" s="17" t="n">
+        <v>574</v>
+      </c>
+      <c r="B577" s="17" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="C577" s="27" t="inlineStr">
+        <is>
+          <t>upload_20260910_184248_1d07e8c4_WhatsApp_Image_2026-08-25_at_10.10.58_AM.jpeg</t>
+        </is>
+      </c>
+      <c r="D577" s="27" t="inlineStr">
+        <is>
+          <t>annotated_20260910_184249_80655ee2_upload_20260910_184248_1d07e8c4_WhatsApp_Image_2026-08-25_at_10.10.58_AM.jpeg</t>
+        </is>
+      </c>
+      <c r="E577" s="27" t="inlineStr">
+        <is>
+          <t>Over-Extrusion</t>
+        </is>
+      </c>
+      <c r="F577" s="28" t="n">
+        <v>0.7969000000000001</v>
+      </c>
+      <c r="G577" s="24" t="inlineStr">
+        <is>
+          <t>DEFECT</t>
+        </is>
+      </c>
+      <c r="H577" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I577" s="31" t="n">
+        <v>326.96</v>
+      </c>
+      <c r="J577" s="17" t="inlineStr">
+        <is>
+          <t>2026-09-10 13:12:49</t>
+        </is>
+      </c>
+      <c r="K577" s="27" t="inlineStr">
+        <is>
+          <t>Web Image Upload</t>
+        </is>
+      </c>
+    </row>
+    <row r="578" ht="19" customHeight="1">
+      <c r="A578" s="18" t="n">
+        <v>575</v>
+      </c>
+      <c r="B578" s="18" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="C578" s="22" t="inlineStr">
+        <is>
+          <t>20260910_210136_a92c5191_auto_defect_20260910_210136.jpg</t>
+        </is>
+      </c>
+      <c r="D578" s="22" t="inlineStr">
+        <is>
+          <t>20260910_210136_a92c5191_auto_defect_20260910_210136.jpg</t>
+        </is>
+      </c>
+      <c r="E578" s="22" t="inlineStr">
+        <is>
+          <t>Spaghetti Failure</t>
+        </is>
+      </c>
+      <c r="F578" s="23" t="n">
+        <v>0.7669</v>
+      </c>
+      <c r="G578" s="24" t="inlineStr">
+        <is>
+          <t>DEFECT</t>
+        </is>
+      </c>
+      <c r="H578" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I578" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J578" s="18" t="inlineStr">
+        <is>
+          <t>2026-09-10 15:31:36</t>
+        </is>
+      </c>
+      <c r="K578" s="22" t="inlineStr">
+        <is>
+          <t>Live Camera 0 (Auto Alert)</t>
+        </is>
+      </c>
+    </row>
+    <row r="579" ht="19" customHeight="1">
+      <c r="A579" s="17" t="n">
+        <v>576</v>
+      </c>
+      <c r="B579" s="17" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="C579" s="27" t="inlineStr">
+        <is>
+          <t>20260910_210140_769f81ec_auto_defect_20260910_210140.jpg</t>
+        </is>
+      </c>
+      <c r="D579" s="27" t="inlineStr">
+        <is>
+          <t>20260910_210140_769f81ec_auto_defect_20260910_210140.jpg</t>
+        </is>
+      </c>
+      <c r="E579" s="27" t="inlineStr">
+        <is>
+          <t>Spaghetti Failure</t>
+        </is>
+      </c>
+      <c r="F579" s="28" t="n">
+        <v>0.5272</v>
+      </c>
+      <c r="G579" s="24" t="inlineStr">
+        <is>
+          <t>DEFECT</t>
+        </is>
+      </c>
+      <c r="H579" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I579" s="31" t="n">
+        <v>73.27</v>
+      </c>
+      <c r="J579" s="17" t="inlineStr">
+        <is>
+          <t>2026-09-10 15:31:40</t>
+        </is>
+      </c>
+      <c r="K579" s="27" t="inlineStr">
+        <is>
+          <t>Live Camera 0 (Auto Alert)</t>
+        </is>
+      </c>
+    </row>
+    <row r="580" ht="19" customHeight="1">
+      <c r="A580" s="18" t="n">
+        <v>577</v>
+      </c>
+      <c r="B580" s="18" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="C580" s="22" t="inlineStr">
+        <is>
+          <t>20260910_210144_d0e307a2_auto_defect_20260910_210144.jpg</t>
+        </is>
+      </c>
+      <c r="D580" s="22" t="inlineStr">
+        <is>
+          <t>20260910_210144_d0e307a2_auto_defect_20260910_210144.jpg</t>
+        </is>
+      </c>
+      <c r="E580" s="22" t="inlineStr">
+        <is>
+          <t>Spaghetti Failure</t>
+        </is>
+      </c>
+      <c r="F580" s="23" t="n">
+        <v>0.5675</v>
+      </c>
+      <c r="G580" s="24" t="inlineStr">
+        <is>
+          <t>DEFECT</t>
+        </is>
+      </c>
+      <c r="H580" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I580" s="26" t="n">
+        <v>63.88</v>
+      </c>
+      <c r="J580" s="18" t="inlineStr">
+        <is>
+          <t>2026-09-10 15:31:44</t>
+        </is>
+      </c>
+      <c r="K580" s="22" t="inlineStr">
+        <is>
+          <t>Live Camera 0 (Auto Alert)</t>
+        </is>
+      </c>
+    </row>
+    <row r="581" ht="19" customHeight="1">
+      <c r="A581" s="17" t="n">
+        <v>578</v>
+      </c>
+      <c r="B581" s="17" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="C581" s="27" t="inlineStr">
+        <is>
+          <t>20260910_210147_8a8ff73a_auto_defect_20260910_210147.jpg</t>
+        </is>
+      </c>
+      <c r="D581" s="27" t="inlineStr">
+        <is>
+          <t>20260910_210147_8a8ff73a_auto_defect_20260910_210147.jpg</t>
+        </is>
+      </c>
+      <c r="E581" s="27" t="inlineStr">
+        <is>
+          <t>Spaghetti Failure</t>
+        </is>
+      </c>
+      <c r="F581" s="28" t="n">
+        <v>0.9206</v>
+      </c>
+      <c r="G581" s="24" t="inlineStr">
+        <is>
+          <t>DEFECT</t>
+        </is>
+      </c>
+      <c r="H581" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="I581" s="31" t="n">
+        <v>73.48</v>
+      </c>
+      <c r="J581" s="17" t="inlineStr">
+        <is>
+          <t>2026-09-10 15:31:47</t>
+        </is>
+      </c>
+      <c r="K581" s="27" t="inlineStr">
+        <is>
+          <t>Live Camera 0 (Auto Alert)</t>
+        </is>
+      </c>
+    </row>
+    <row r="582" ht="19" customHeight="1">
+      <c r="A582" s="18" t="n">
+        <v>579</v>
+      </c>
+      <c r="B582" s="18" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="C582" s="22" t="inlineStr">
+        <is>
+          <t>20260910_210150_32c8f780_auto_defect_20260910_210150.jpg</t>
+        </is>
+      </c>
+      <c r="D582" s="22" t="inlineStr">
+        <is>
+          <t>20260910_210150_32c8f780_auto_defect_20260910_210150.jpg</t>
+        </is>
+      </c>
+      <c r="E582" s="22" t="inlineStr">
+        <is>
+          <t>Spaghetti Failure</t>
+        </is>
+      </c>
+      <c r="F582" s="23" t="n">
+        <v>0.7591</v>
+      </c>
+      <c r="G582" s="24" t="inlineStr">
+        <is>
+          <t>DEFECT</t>
+        </is>
+      </c>
+      <c r="H582" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="I582" s="26" t="n">
+        <v>65.52</v>
+      </c>
+      <c r="J582" s="18" t="inlineStr">
+        <is>
+          <t>2026-09-10 15:31:50</t>
+        </is>
+      </c>
+      <c r="K582" s="22" t="inlineStr">
+        <is>
+          <t>Live Camera 0 (Auto Alert)</t>
+        </is>
+      </c>
+    </row>
+    <row r="583" ht="19" customHeight="1">
+      <c r="A583" s="17" t="n">
+        <v>580</v>
+      </c>
+      <c r="B583" s="17" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="C583" s="27" t="inlineStr">
+        <is>
+          <t>test_sample.jpg</t>
+        </is>
+      </c>
+      <c r="D583" s="27" t="inlineStr">
+        <is>
+          <t>annotated_test_sample.jpg</t>
+        </is>
+      </c>
+      <c r="E583" s="27" t="inlineStr">
+        <is>
+          <t>Stringing</t>
+        </is>
+      </c>
+      <c r="F583" s="28" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="G583" s="24" t="inlineStr">
+        <is>
+          <t>DEFECT</t>
+        </is>
+      </c>
+      <c r="H583" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I583" s="31" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="J583" s="17" t="inlineStr">
+        <is>
+          <t>2026-09-10 15:43:21</t>
+        </is>
+      </c>
+      <c r="K583" s="27" t="inlineStr">
+        <is>
+          <t>Unit Test</t>
+        </is>
+      </c>
+    </row>
+    <row r="584" ht="19" customHeight="1">
+      <c r="A584" s="18" t="n">
+        <v>581</v>
+      </c>
+      <c r="B584" s="18" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="C584" s="22" t="inlineStr">
+        <is>
+          <t>test_sample.jpg</t>
+        </is>
+      </c>
+      <c r="D584" s="22" t="inlineStr">
+        <is>
+          <t>annotated_test_sample.jpg</t>
+        </is>
+      </c>
+      <c r="E584" s="22" t="inlineStr">
+        <is>
+          <t>Stringing</t>
+        </is>
+      </c>
+      <c r="F584" s="23" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="G584" s="24" t="inlineStr">
+        <is>
+          <t>DEFECT</t>
+        </is>
+      </c>
+      <c r="H584" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I584" s="26" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="J584" s="18" t="inlineStr">
+        <is>
+          <t>2026-09-10 15:50:04</t>
+        </is>
+      </c>
+      <c r="K584" s="22" t="inlineStr">
+        <is>
+          <t>Unit Test</t>
         </is>
       </c>
     </row>
@@ -28183,7 +29555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L654"/>
+  <dimension ref="A1:L674"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -28203,7 +29575,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>DETAILED LOCALIZED DEFECT BOUNDING BOXES (651 DETECTIONS)</t>
+          <t>DETAILED LOCALIZED DEFECT BOUNDING BOXES (671 DETECTIONS)</t>
         </is>
       </c>
     </row>
@@ -55610,6 +56982,846 @@
       </c>
       <c r="L654" s="32" t="n">
         <v>51460.92</v>
+      </c>
+    </row>
+    <row r="655" ht="19" customHeight="1">
+      <c r="A655" s="17" t="n">
+        <v>652</v>
+      </c>
+      <c r="B655" s="17" t="n">
+        <v>554</v>
+      </c>
+      <c r="C655" s="17" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="D655" s="27" t="inlineStr">
+        <is>
+          <t>Spaghetti Failure</t>
+        </is>
+      </c>
+      <c r="E655" s="28" t="n">
+        <v>0.8611</v>
+      </c>
+      <c r="F655" s="33" t="n">
+        <v>399.1</v>
+      </c>
+      <c r="G655" s="33" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="H655" s="33" t="n">
+        <v>640</v>
+      </c>
+      <c r="I655" s="33" t="n">
+        <v>302.2</v>
+      </c>
+      <c r="J655" s="33" t="n">
+        <v>240.9</v>
+      </c>
+      <c r="K655" s="33" t="n">
+        <v>248.1</v>
+      </c>
+      <c r="L655" s="33" t="n">
+        <v>59767.29</v>
+      </c>
+    </row>
+    <row r="656" ht="19" customHeight="1">
+      <c r="A656" s="18" t="n">
+        <v>653</v>
+      </c>
+      <c r="B656" s="18" t="n">
+        <v>555</v>
+      </c>
+      <c r="C656" s="18" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="D656" s="22" t="inlineStr">
+        <is>
+          <t>Spaghetti Failure</t>
+        </is>
+      </c>
+      <c r="E656" s="23" t="n">
+        <v>0.6252</v>
+      </c>
+      <c r="F656" s="32" t="n">
+        <v>307.7</v>
+      </c>
+      <c r="G656" s="32" t="n">
+        <v>140</v>
+      </c>
+      <c r="H656" s="32" t="n">
+        <v>547.6</v>
+      </c>
+      <c r="I656" s="32" t="n">
+        <v>467.7</v>
+      </c>
+      <c r="J656" s="32" t="n">
+        <v>239.9</v>
+      </c>
+      <c r="K656" s="32" t="n">
+        <v>327.7</v>
+      </c>
+      <c r="L656" s="32" t="n">
+        <v>78615.23</v>
+      </c>
+    </row>
+    <row r="657" ht="19" customHeight="1">
+      <c r="A657" s="17" t="n">
+        <v>654</v>
+      </c>
+      <c r="B657" s="17" t="n">
+        <v>556</v>
+      </c>
+      <c r="C657" s="17" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="D657" s="27" t="inlineStr">
+        <is>
+          <t>Spaghetti Failure</t>
+        </is>
+      </c>
+      <c r="E657" s="28" t="n">
+        <v>0.5371</v>
+      </c>
+      <c r="F657" s="33" t="n">
+        <v>305</v>
+      </c>
+      <c r="G657" s="33" t="n">
+        <v>183.8</v>
+      </c>
+      <c r="H657" s="33" t="n">
+        <v>532.2</v>
+      </c>
+      <c r="I657" s="33" t="n">
+        <v>472.3</v>
+      </c>
+      <c r="J657" s="33" t="n">
+        <v>227.2</v>
+      </c>
+      <c r="K657" s="33" t="n">
+        <v>288.5</v>
+      </c>
+      <c r="L657" s="33" t="n">
+        <v>65547.2</v>
+      </c>
+    </row>
+    <row r="658" ht="19" customHeight="1">
+      <c r="A658" s="18" t="n">
+        <v>655</v>
+      </c>
+      <c r="B658" s="18" t="n">
+        <v>558</v>
+      </c>
+      <c r="C658" s="18" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="D658" s="22" t="inlineStr">
+        <is>
+          <t>Stringing</t>
+        </is>
+      </c>
+      <c r="E658" s="23" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="F658" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="G658" s="32" t="n">
+        <v>20</v>
+      </c>
+      <c r="H658" s="32" t="n">
+        <v>100</v>
+      </c>
+      <c r="I658" s="32" t="n">
+        <v>150</v>
+      </c>
+      <c r="J658" s="32" t="n">
+        <v>90</v>
+      </c>
+      <c r="K658" s="32" t="n">
+        <v>130</v>
+      </c>
+      <c r="L658" s="32" t="n">
+        <v>11700</v>
+      </c>
+    </row>
+    <row r="659" ht="19" customHeight="1">
+      <c r="A659" s="17" t="n">
+        <v>656</v>
+      </c>
+      <c r="B659" s="17" t="n">
+        <v>561</v>
+      </c>
+      <c r="C659" s="17" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="D659" s="27" t="inlineStr">
+        <is>
+          <t>Stringing</t>
+        </is>
+      </c>
+      <c r="E659" s="28" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="F659" s="33" t="n">
+        <v>10</v>
+      </c>
+      <c r="G659" s="33" t="n">
+        <v>20</v>
+      </c>
+      <c r="H659" s="33" t="n">
+        <v>100</v>
+      </c>
+      <c r="I659" s="33" t="n">
+        <v>150</v>
+      </c>
+      <c r="J659" s="33" t="n">
+        <v>90</v>
+      </c>
+      <c r="K659" s="33" t="n">
+        <v>130</v>
+      </c>
+      <c r="L659" s="33" t="n">
+        <v>11700</v>
+      </c>
+    </row>
+    <row r="660" ht="19" customHeight="1">
+      <c r="A660" s="18" t="n">
+        <v>657</v>
+      </c>
+      <c r="B660" s="18" t="n">
+        <v>564</v>
+      </c>
+      <c r="C660" s="18" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="D660" s="22" t="inlineStr">
+        <is>
+          <t>Stringing</t>
+        </is>
+      </c>
+      <c r="E660" s="23" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="F660" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="G660" s="32" t="n">
+        <v>20</v>
+      </c>
+      <c r="H660" s="32" t="n">
+        <v>100</v>
+      </c>
+      <c r="I660" s="32" t="n">
+        <v>150</v>
+      </c>
+      <c r="J660" s="32" t="n">
+        <v>90</v>
+      </c>
+      <c r="K660" s="32" t="n">
+        <v>130</v>
+      </c>
+      <c r="L660" s="32" t="n">
+        <v>11700</v>
+      </c>
+    </row>
+    <row r="661" ht="19" customHeight="1">
+      <c r="A661" s="17" t="n">
+        <v>658</v>
+      </c>
+      <c r="B661" s="17" t="n">
+        <v>567</v>
+      </c>
+      <c r="C661" s="17" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="D661" s="27" t="inlineStr">
+        <is>
+          <t>Stringing</t>
+        </is>
+      </c>
+      <c r="E661" s="28" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="F661" s="33" t="n">
+        <v>10</v>
+      </c>
+      <c r="G661" s="33" t="n">
+        <v>20</v>
+      </c>
+      <c r="H661" s="33" t="n">
+        <v>100</v>
+      </c>
+      <c r="I661" s="33" t="n">
+        <v>150</v>
+      </c>
+      <c r="J661" s="33" t="n">
+        <v>90</v>
+      </c>
+      <c r="K661" s="33" t="n">
+        <v>130</v>
+      </c>
+      <c r="L661" s="33" t="n">
+        <v>11700</v>
+      </c>
+    </row>
+    <row r="662" ht="19" customHeight="1">
+      <c r="A662" s="18" t="n">
+        <v>659</v>
+      </c>
+      <c r="B662" s="18" t="n">
+        <v>570</v>
+      </c>
+      <c r="C662" s="18" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="D662" s="22" t="inlineStr">
+        <is>
+          <t>Stringing</t>
+        </is>
+      </c>
+      <c r="E662" s="23" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="F662" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="G662" s="32" t="n">
+        <v>20</v>
+      </c>
+      <c r="H662" s="32" t="n">
+        <v>100</v>
+      </c>
+      <c r="I662" s="32" t="n">
+        <v>150</v>
+      </c>
+      <c r="J662" s="32" t="n">
+        <v>90</v>
+      </c>
+      <c r="K662" s="32" t="n">
+        <v>130</v>
+      </c>
+      <c r="L662" s="32" t="n">
+        <v>11700</v>
+      </c>
+    </row>
+    <row r="663" ht="19" customHeight="1">
+      <c r="A663" s="17" t="n">
+        <v>660</v>
+      </c>
+      <c r="B663" s="17" t="n">
+        <v>572</v>
+      </c>
+      <c r="C663" s="17" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="D663" s="27" t="inlineStr">
+        <is>
+          <t>Spaghetti Failure</t>
+        </is>
+      </c>
+      <c r="E663" s="28" t="n">
+        <v>0.9859</v>
+      </c>
+      <c r="F663" s="33" t="n">
+        <v>65</v>
+      </c>
+      <c r="G663" s="33" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="H663" s="33" t="n">
+        <v>334.5</v>
+      </c>
+      <c r="I663" s="33" t="n">
+        <v>274.2</v>
+      </c>
+      <c r="J663" s="33" t="n">
+        <v>269.5</v>
+      </c>
+      <c r="K663" s="33" t="n">
+        <v>246.4</v>
+      </c>
+      <c r="L663" s="33" t="n">
+        <v>66404.8</v>
+      </c>
+    </row>
+    <row r="664" ht="19" customHeight="1">
+      <c r="A664" s="18" t="n">
+        <v>661</v>
+      </c>
+      <c r="B664" s="18" t="n">
+        <v>573</v>
+      </c>
+      <c r="C664" s="18" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="D664" s="22" t="inlineStr">
+        <is>
+          <t>Spaghetti Failure</t>
+        </is>
+      </c>
+      <c r="E664" s="23" t="n">
+        <v>0.8398</v>
+      </c>
+      <c r="F664" s="32" t="n">
+        <v>401.1</v>
+      </c>
+      <c r="G664" s="32" t="n">
+        <v>158.6</v>
+      </c>
+      <c r="H664" s="32" t="n">
+        <v>967.6</v>
+      </c>
+      <c r="I664" s="32" t="n">
+        <v>627.8</v>
+      </c>
+      <c r="J664" s="32" t="n">
+        <v>566.5</v>
+      </c>
+      <c r="K664" s="32" t="n">
+        <v>469.2</v>
+      </c>
+      <c r="L664" s="32" t="n">
+        <v>265801.8</v>
+      </c>
+    </row>
+    <row r="665" ht="19" customHeight="1">
+      <c r="A665" s="17" t="n">
+        <v>662</v>
+      </c>
+      <c r="B665" s="17" t="n">
+        <v>574</v>
+      </c>
+      <c r="C665" s="17" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="D665" s="27" t="inlineStr">
+        <is>
+          <t>Over-Extrusion</t>
+        </is>
+      </c>
+      <c r="E665" s="28" t="n">
+        <v>0.7969000000000001</v>
+      </c>
+      <c r="F665" s="33" t="n">
+        <v>1003.9</v>
+      </c>
+      <c r="G665" s="33" t="n">
+        <v>155.6</v>
+      </c>
+      <c r="H665" s="33" t="n">
+        <v>1415.3</v>
+      </c>
+      <c r="I665" s="33" t="n">
+        <v>546.7</v>
+      </c>
+      <c r="J665" s="33" t="n">
+        <v>411.4</v>
+      </c>
+      <c r="K665" s="33" t="n">
+        <v>391.1</v>
+      </c>
+      <c r="L665" s="33" t="n">
+        <v>160898.54</v>
+      </c>
+    </row>
+    <row r="666" ht="19" customHeight="1">
+      <c r="A666" s="18" t="n">
+        <v>663</v>
+      </c>
+      <c r="B666" s="18" t="n">
+        <v>575</v>
+      </c>
+      <c r="C666" s="18" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="D666" s="22" t="inlineStr">
+        <is>
+          <t>Spaghetti Failure</t>
+        </is>
+      </c>
+      <c r="E666" s="23" t="n">
+        <v>0.7669</v>
+      </c>
+      <c r="F666" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G666" s="32" t="n">
+        <v>228.1</v>
+      </c>
+      <c r="H666" s="32" t="n">
+        <v>209.3</v>
+      </c>
+      <c r="I666" s="32" t="n">
+        <v>468.1</v>
+      </c>
+      <c r="J666" s="32" t="n">
+        <v>209.3</v>
+      </c>
+      <c r="K666" s="32" t="n">
+        <v>240</v>
+      </c>
+      <c r="L666" s="32" t="n">
+        <v>50232</v>
+      </c>
+    </row>
+    <row r="667" ht="19" customHeight="1">
+      <c r="A667" s="17" t="n">
+        <v>664</v>
+      </c>
+      <c r="B667" s="17" t="n">
+        <v>576</v>
+      </c>
+      <c r="C667" s="17" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="D667" s="27" t="inlineStr">
+        <is>
+          <t>Spaghetti Failure</t>
+        </is>
+      </c>
+      <c r="E667" s="28" t="n">
+        <v>0.5272</v>
+      </c>
+      <c r="F667" s="33" t="n">
+        <v>225.6</v>
+      </c>
+      <c r="G667" s="33" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="H667" s="33" t="n">
+        <v>418.6</v>
+      </c>
+      <c r="I667" s="33" t="n">
+        <v>275.6</v>
+      </c>
+      <c r="J667" s="33" t="n">
+        <v>193</v>
+      </c>
+      <c r="K667" s="33" t="n">
+        <v>226.5</v>
+      </c>
+      <c r="L667" s="33" t="n">
+        <v>43714.5</v>
+      </c>
+    </row>
+    <row r="668" ht="19" customHeight="1">
+      <c r="A668" s="18" t="n">
+        <v>665</v>
+      </c>
+      <c r="B668" s="18" t="n">
+        <v>577</v>
+      </c>
+      <c r="C668" s="18" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="D668" s="22" t="inlineStr">
+        <is>
+          <t>Spaghetti Failure</t>
+        </is>
+      </c>
+      <c r="E668" s="23" t="n">
+        <v>0.5675</v>
+      </c>
+      <c r="F668" s="32" t="n">
+        <v>236.5</v>
+      </c>
+      <c r="G668" s="32" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="H668" s="32" t="n">
+        <v>418.8</v>
+      </c>
+      <c r="I668" s="32" t="n">
+        <v>271.2</v>
+      </c>
+      <c r="J668" s="32" t="n">
+        <v>182.3</v>
+      </c>
+      <c r="K668" s="32" t="n">
+        <v>229</v>
+      </c>
+      <c r="L668" s="32" t="n">
+        <v>41746.7</v>
+      </c>
+    </row>
+    <row r="669" ht="19" customHeight="1">
+      <c r="A669" s="17" t="n">
+        <v>666</v>
+      </c>
+      <c r="B669" s="17" t="n">
+        <v>578</v>
+      </c>
+      <c r="C669" s="17" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="D669" s="27" t="inlineStr">
+        <is>
+          <t>Spaghetti Failure</t>
+        </is>
+      </c>
+      <c r="E669" s="28" t="n">
+        <v>0.9206</v>
+      </c>
+      <c r="F669" s="33" t="n">
+        <v>280.1</v>
+      </c>
+      <c r="G669" s="33" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="H669" s="33" t="n">
+        <v>480.6</v>
+      </c>
+      <c r="I669" s="33" t="n">
+        <v>270.3</v>
+      </c>
+      <c r="J669" s="33" t="n">
+        <v>200.5</v>
+      </c>
+      <c r="K669" s="33" t="n">
+        <v>241.5</v>
+      </c>
+      <c r="L669" s="33" t="n">
+        <v>48420.75</v>
+      </c>
+    </row>
+    <row r="670" ht="19" customHeight="1">
+      <c r="A670" s="18" t="n">
+        <v>667</v>
+      </c>
+      <c r="B670" s="18" t="n">
+        <v>578</v>
+      </c>
+      <c r="C670" s="18" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="D670" s="22" t="inlineStr">
+        <is>
+          <t>Spaghetti Failure</t>
+        </is>
+      </c>
+      <c r="E670" s="23" t="n">
+        <v>0.5104</v>
+      </c>
+      <c r="F670" s="32" t="n">
+        <v>145.9</v>
+      </c>
+      <c r="G670" s="32" t="n">
+        <v>195.6</v>
+      </c>
+      <c r="H670" s="32" t="n">
+        <v>465.1</v>
+      </c>
+      <c r="I670" s="32" t="n">
+        <v>476.4</v>
+      </c>
+      <c r="J670" s="32" t="n">
+        <v>319.2</v>
+      </c>
+      <c r="K670" s="32" t="n">
+        <v>280.8</v>
+      </c>
+      <c r="L670" s="32" t="n">
+        <v>89631.36</v>
+      </c>
+    </row>
+    <row r="671" ht="19" customHeight="1">
+      <c r="A671" s="17" t="n">
+        <v>668</v>
+      </c>
+      <c r="B671" s="17" t="n">
+        <v>579</v>
+      </c>
+      <c r="C671" s="17" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="D671" s="27" t="inlineStr">
+        <is>
+          <t>Spaghetti Failure</t>
+        </is>
+      </c>
+      <c r="E671" s="28" t="n">
+        <v>0.7591</v>
+      </c>
+      <c r="F671" s="33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G671" s="33" t="n">
+        <v>192.2</v>
+      </c>
+      <c r="H671" s="33" t="n">
+        <v>171.6</v>
+      </c>
+      <c r="I671" s="33" t="n">
+        <v>422.5</v>
+      </c>
+      <c r="J671" s="33" t="n">
+        <v>171.6</v>
+      </c>
+      <c r="K671" s="33" t="n">
+        <v>230.3</v>
+      </c>
+      <c r="L671" s="33" t="n">
+        <v>39519.48</v>
+      </c>
+    </row>
+    <row r="672" ht="19" customHeight="1">
+      <c r="A672" s="18" t="n">
+        <v>669</v>
+      </c>
+      <c r="B672" s="18" t="n">
+        <v>579</v>
+      </c>
+      <c r="C672" s="18" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="D672" s="22" t="inlineStr">
+        <is>
+          <t>Spaghetti Failure</t>
+        </is>
+      </c>
+      <c r="E672" s="23" t="n">
+        <v>0.736</v>
+      </c>
+      <c r="F672" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G672" s="32" t="n">
+        <v>192</v>
+      </c>
+      <c r="H672" s="32" t="n">
+        <v>375.9</v>
+      </c>
+      <c r="I672" s="32" t="n">
+        <v>428.7</v>
+      </c>
+      <c r="J672" s="32" t="n">
+        <v>375.9</v>
+      </c>
+      <c r="K672" s="32" t="n">
+        <v>236.7</v>
+      </c>
+      <c r="L672" s="32" t="n">
+        <v>88975.53</v>
+      </c>
+    </row>
+    <row r="673" ht="19" customHeight="1">
+      <c r="A673" s="17" t="n">
+        <v>670</v>
+      </c>
+      <c r="B673" s="17" t="n">
+        <v>580</v>
+      </c>
+      <c r="C673" s="17" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="D673" s="27" t="inlineStr">
+        <is>
+          <t>Stringing</t>
+        </is>
+      </c>
+      <c r="E673" s="28" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="F673" s="33" t="n">
+        <v>10</v>
+      </c>
+      <c r="G673" s="33" t="n">
+        <v>20</v>
+      </c>
+      <c r="H673" s="33" t="n">
+        <v>100</v>
+      </c>
+      <c r="I673" s="33" t="n">
+        <v>150</v>
+      </c>
+      <c r="J673" s="33" t="n">
+        <v>90</v>
+      </c>
+      <c r="K673" s="33" t="n">
+        <v>130</v>
+      </c>
+      <c r="L673" s="33" t="n">
+        <v>11700</v>
+      </c>
+    </row>
+    <row r="674" ht="19" customHeight="1">
+      <c r="A674" s="18" t="n">
+        <v>671</v>
+      </c>
+      <c r="B674" s="18" t="n">
+        <v>581</v>
+      </c>
+      <c r="C674" s="18" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="D674" s="22" t="inlineStr">
+        <is>
+          <t>Stringing</t>
+        </is>
+      </c>
+      <c r="E674" s="23" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="F674" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="G674" s="32" t="n">
+        <v>20</v>
+      </c>
+      <c r="H674" s="32" t="n">
+        <v>100</v>
+      </c>
+      <c r="I674" s="32" t="n">
+        <v>150</v>
+      </c>
+      <c r="J674" s="32" t="n">
+        <v>90</v>
+      </c>
+      <c r="K674" s="32" t="n">
+        <v>130</v>
+      </c>
+      <c r="L674" s="32" t="n">
+        <v>11700</v>
       </c>
     </row>
   </sheetData>
